--- a/saffmatchreports.xlsx
+++ b/saffmatchreports.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvarolopezmolina/Desktop/alnassracademy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvarolopezmolina/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D954D3ED-5C0C-344D-B0E6-40C04F9D3D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1155C30C-56E3-6649-B4E4-4EEC92DB57F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
   <si>
     <t>Scout Name</t>
   </si>
@@ -61,12 +61,6 @@
     <t>Alvaro</t>
   </si>
   <si>
-    <t>Rafa Habibi</t>
-  </si>
-  <si>
-    <t>CM</t>
-  </si>
-  <si>
     <t>Saudi Elite League U-21</t>
   </si>
   <si>
@@ -89,6 +83,18 @@
   </si>
   <si>
     <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Rafa</t>
+  </si>
+  <si>
+    <t>Maher Mohammed Abdu Tawashi</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>DF</t>
   </si>
 </sst>
 </file>
@@ -156,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -164,6 +170,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -466,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -507,7 +514,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -515,19 +522,19 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2">
+        <v>2008</v>
+      </c>
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
-      </c>
-      <c r="D2">
-        <v>2007</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -536,19 +543,101 @@
         <v>3</v>
       </c>
       <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>20</v>
       </c>
-      <c r="M2" t="s">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
         <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3">
+        <v>2008</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>2008</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="3">
+        <v>45936</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
